--- a/output/yearly_benthic_cover_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_8_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.0538721695703</v>
+        <v>45.58336282495405</v>
       </c>
       <c r="M2" t="n">
-        <v>100.441165550098</v>
+        <v>99.88509544642966</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04717416463859</v>
+        <v>87.99676142002549</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90185347670784</v>
+        <v>45.92663640213999</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228801909919095</v>
+        <v>2.228653782393305</v>
       </c>
       <c r="E3" t="n">
-        <v>5.692247429527063</v>
+        <v>5.703457350400984</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429339699730316</v>
+        <v>0.7428845941311016</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9635744812945</v>
+        <v>33.97274257733766</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17496261875945</v>
+        <v>34.17269133003067</v>
       </c>
       <c r="I3" t="n">
-        <v>6.601316442833984</v>
+        <v>6.533303072412396</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643337312331448</v>
+        <v>4.643028713319385</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95282583536142</v>
+        <v>12.00323857997449</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90837485928781</v>
+        <v>48.83560485601824</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630541713571</v>
+        <v>106.7654798381327</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.24912632314339</v>
+        <v>87.08402189117612</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74635945516766</v>
+        <v>42.6424019799154</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190940136363825</v>
+        <v>2.184663724769492</v>
       </c>
       <c r="E4" t="n">
-        <v>6.514330863668831</v>
+        <v>6.500178389617345</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444986692792007</v>
+        <v>0.7444359776731505</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38661824287088</v>
+        <v>33.30217502870246</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24693878684323</v>
+        <v>34.24405497296492</v>
       </c>
       <c r="I4" t="n">
-        <v>5.512682941122401</v>
+        <v>5.455788936991565</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653116682995005</v>
+        <v>4.652724860457191</v>
       </c>
       <c r="K4" t="n">
-        <v>12.75087367685661</v>
+        <v>12.91597810882386</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31939696678589</v>
+        <v>44.26013927036038</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81663009881017</v>
+        <v>99.81851935909965</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.14806159106979</v>
+        <v>85.82988322585027</v>
       </c>
       <c r="C5" t="n">
-        <v>42.50097358859834</v>
+        <v>42.23506291890764</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137427542792058</v>
+        <v>2.123157379369241</v>
       </c>
       <c r="E5" t="n">
-        <v>7.122235452662215</v>
+        <v>7.07626316724916</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458243885983475</v>
+        <v>0.7457527521597039</v>
       </c>
       <c r="G5" t="n">
-        <v>32.57116714810403</v>
+        <v>32.36459591450213</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30792187552399</v>
+        <v>34.30462659934638</v>
       </c>
       <c r="I5" t="n">
-        <v>4.60208275464948</v>
+        <v>4.554532712225503</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661402428739673</v>
+        <v>4.66095470099815</v>
       </c>
       <c r="K5" t="n">
-        <v>13.85193840893023</v>
+        <v>14.17011677414972</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49395792077357</v>
+        <v>43.44327061424841</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84686991830213</v>
+        <v>99.84845030730578</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.87907912717273</v>
+        <v>84.33766347947692</v>
       </c>
       <c r="C6" t="n">
-        <v>41.94685022862761</v>
+        <v>41.45012345471599</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075712630663725</v>
+        <v>2.050007587470439</v>
       </c>
       <c r="E6" t="n">
-        <v>7.556734200290773</v>
+        <v>7.465986840287051</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469493624418035</v>
+        <v>0.7468731353862412</v>
       </c>
       <c r="G6" t="n">
-        <v>31.63072510821305</v>
+        <v>31.24952857232613</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35967067232296</v>
+        <v>34.35616422776709</v>
       </c>
       <c r="I6" t="n">
-        <v>3.840853637979152</v>
+        <v>3.801146020075959</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668433515261273</v>
+        <v>4.667957096164009</v>
       </c>
       <c r="K6" t="n">
-        <v>15.12092087282725</v>
+        <v>15.66233652052307</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80439326647156</v>
+        <v>42.76102522719911</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87216436792642</v>
+        <v>99.87348520243818</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.39715234494233</v>
+        <v>82.50025752565082</v>
       </c>
       <c r="C7" t="n">
-        <v>41.0616464135427</v>
+        <v>40.20292712887654</v>
       </c>
       <c r="D7" t="n">
-        <v>2.003728805528557</v>
+        <v>1.960117166540159</v>
       </c>
       <c r="E7" t="n">
-        <v>7.8288087507638</v>
+        <v>7.667225590464953</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479061623990451</v>
+        <v>0.7478302407970989</v>
       </c>
       <c r="G7" t="n">
-        <v>30.53380034538589</v>
+        <v>29.87927350868251</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40368347035607</v>
+        <v>34.40019107666654</v>
       </c>
       <c r="I7" t="n">
-        <v>3.204811295514928</v>
+        <v>3.171680937517698</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674413514994033</v>
+        <v>4.67393900498187</v>
       </c>
       <c r="K7" t="n">
-        <v>16.60284765505767</v>
+        <v>17.49974247434916</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22881555256686</v>
+        <v>42.19174300732773</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89330962116722</v>
+        <v>99.89441261055343</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.29954952321606</v>
+        <v>87.36462238972297</v>
       </c>
       <c r="C8" t="n">
-        <v>43.39483688352741</v>
+        <v>42.55308629697674</v>
       </c>
       <c r="D8" t="n">
-        <v>2.008003061826021</v>
+        <v>1.964278392752406</v>
       </c>
       <c r="E8" t="n">
-        <v>9.683074363138061</v>
+        <v>9.528300036599326</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495015592490206</v>
+        <v>0.7494178452798499</v>
       </c>
       <c r="G8" t="n">
-        <v>31.04682564317018</v>
+        <v>30.40142799863235</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47707172545495</v>
+        <v>34.47322088287309</v>
       </c>
       <c r="I8" t="n">
-        <v>5.650688425071452</v>
+        <v>5.564115700586884</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68438474530638</v>
+        <v>4.683861532999064</v>
       </c>
       <c r="K8" t="n">
-        <v>11.70045047678393</v>
+        <v>12.63537761027703</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71675729600031</v>
+        <v>44.62645847948499</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81204465631164</v>
+        <v>99.81492238673877</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.38059070264133</v>
+        <v>85.06619463990621</v>
       </c>
       <c r="C9" t="n">
-        <v>42.353263643624</v>
+        <v>41.11779037075092</v>
       </c>
       <c r="D9" t="n">
-        <v>1.921333743652123</v>
+        <v>1.859891614616718</v>
       </c>
       <c r="E9" t="n">
-        <v>10.05138057593582</v>
+        <v>9.796142311035021</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508659699377447</v>
+        <v>0.7507819586759821</v>
       </c>
       <c r="G9" t="n">
-        <v>29.70678425523001</v>
+        <v>28.78581835225502</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53983461713626</v>
+        <v>34.53597009909517</v>
       </c>
       <c r="I9" t="n">
-        <v>4.71747922863845</v>
+        <v>4.645203062503418</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692912312110906</v>
+        <v>4.69238724172489</v>
       </c>
       <c r="K9" t="n">
-        <v>13.61940929735869</v>
+        <v>14.93380536009378</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87036349165421</v>
+        <v>43.79384549969456</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84303643263689</v>
+        <v>99.84544123053925</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.31325131286893</v>
+        <v>82.56981517845034</v>
       </c>
       <c r="C10" t="n">
-        <v>41.01823060340535</v>
+        <v>39.34142186714126</v>
       </c>
       <c r="D10" t="n">
-        <v>1.828876389239402</v>
+        <v>1.747816269560844</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22391899210556</v>
+        <v>9.852012738780223</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520347952114778</v>
+        <v>0.7519570562494757</v>
       </c>
       <c r="G10" t="n">
-        <v>28.27725089621703</v>
+        <v>27.05121161539443</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59360057972798</v>
+        <v>34.59002458747588</v>
       </c>
       <c r="I10" t="n">
-        <v>3.937352190295762</v>
+        <v>3.877061309430279</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700217470071737</v>
+        <v>4.699731601559225</v>
       </c>
       <c r="K10" t="n">
-        <v>15.68674868713105</v>
+        <v>17.43018482154963</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16397961977921</v>
+        <v>43.09935989290624</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86895891031561</v>
+        <v>99.87096658159714</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.112018240239</v>
+        <v>79.83630572181285</v>
       </c>
       <c r="C11" t="n">
-        <v>39.42770247101794</v>
+        <v>37.20796896076833</v>
       </c>
       <c r="D11" t="n">
-        <v>1.731361572471062</v>
+        <v>1.626399776929112</v>
       </c>
       <c r="E11" t="n">
-        <v>10.22636834498813</v>
+        <v>9.706825780942523</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530378203657242</v>
+        <v>0.7529727879731818</v>
       </c>
       <c r="G11" t="n">
-        <v>26.76952136562596</v>
+        <v>25.17203055215532</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63973973682331</v>
+        <v>34.63674824676636</v>
       </c>
       <c r="I11" t="n">
-        <v>3.285503022679021</v>
+        <v>3.23524865221396</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706486377285778</v>
+        <v>4.706079924832388</v>
       </c>
       <c r="K11" t="n">
-        <v>17.887981759761</v>
+        <v>20.16369427818715</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57494487504618</v>
+        <v>42.52064061356035</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89062910582513</v>
+        <v>99.89230385251582</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.64913595445771</v>
+        <v>77.11408679467996</v>
       </c>
       <c r="C12" t="n">
-        <v>37.47372668193055</v>
+        <v>34.98535006145252</v>
       </c>
       <c r="D12" t="n">
-        <v>1.623114421739425</v>
+        <v>1.506874263176921</v>
       </c>
       <c r="E12" t="n">
-        <v>10.0438447981547</v>
+        <v>9.443327191834486</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539016597505991</v>
+        <v>0.7538513190797098</v>
       </c>
       <c r="G12" t="n">
-        <v>25.09585339219223</v>
+        <v>23.32211644947812</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67947634852756</v>
+        <v>34.67716067766665</v>
       </c>
       <c r="I12" t="n">
-        <v>2.741059960651952</v>
+        <v>2.699186149195886</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711885373441246</v>
+        <v>4.711570744248188</v>
       </c>
       <c r="K12" t="n">
-        <v>20.3508640455423</v>
+        <v>22.88591320532004</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08414529967494</v>
+        <v>42.03886871511038</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9087360271478</v>
+        <v>99.91013198188296</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.26142705636254</v>
+        <v>74.51132304054471</v>
       </c>
       <c r="C13" t="n">
-        <v>35.50970814605454</v>
+        <v>32.79829243460011</v>
       </c>
       <c r="D13" t="n">
-        <v>1.519191871964406</v>
+        <v>1.393839340445018</v>
       </c>
       <c r="E13" t="n">
-        <v>9.781849565524666</v>
+        <v>9.110220947527038</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546453570663076</v>
+        <v>0.7546106498360434</v>
       </c>
       <c r="G13" t="n">
-        <v>23.48905042231795</v>
+        <v>21.57265818661464</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71368642505015</v>
+        <v>34.712089892458</v>
       </c>
       <c r="I13" t="n">
-        <v>2.286469932774619</v>
+        <v>2.251587462188711</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716533481664425</v>
+        <v>4.716316561475273</v>
       </c>
       <c r="K13" t="n">
-        <v>22.73857294363749</v>
+        <v>25.48867695945527</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67557835584543</v>
+        <v>41.63805321291142</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92385944553746</v>
+        <v>99.92502260696681</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.91323919784446</v>
+        <v>82.07699792677528</v>
       </c>
       <c r="C14" t="n">
-        <v>39.57477369917196</v>
+        <v>37.67165429041095</v>
       </c>
       <c r="D14" t="n">
-        <v>1.52103198950015</v>
+        <v>1.395364494760864</v>
       </c>
       <c r="E14" t="n">
-        <v>12.06525601238048</v>
+        <v>11.76752408443074</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555594194572613</v>
+        <v>0.7554363530975206</v>
       </c>
       <c r="G14" t="n">
-        <v>25.28086112819815</v>
+        <v>23.79455009602101</v>
       </c>
       <c r="H14" t="n">
-        <v>36.51909294454818</v>
+        <v>36.94835911235665</v>
       </c>
       <c r="I14" t="n">
-        <v>3.049191332152347</v>
+        <v>2.694286579248989</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722246371607886</v>
+        <v>4.721477206859506</v>
       </c>
       <c r="K14" t="n">
-        <v>16.08676080215556</v>
+        <v>17.92300207322471</v>
       </c>
       <c r="L14" t="n">
-        <v>44.23694874952131</v>
+        <v>44.3156322469104</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89848325084883</v>
+        <v>99.91028861054606</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.13404567993781</v>
+        <v>81.13826058945153</v>
       </c>
       <c r="C15" t="n">
-        <v>39.2670138277617</v>
+        <v>37.1295060581282</v>
       </c>
       <c r="D15" t="n">
-        <v>1.492059090562579</v>
+        <v>1.359556404257879</v>
       </c>
       <c r="E15" t="n">
-        <v>12.25936549309896</v>
+        <v>11.85277803730321</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563299938693752</v>
+        <v>0.7561360180286354</v>
       </c>
       <c r="G15" t="n">
-        <v>24.79930660496766</v>
+        <v>23.19542395328467</v>
       </c>
       <c r="H15" t="n">
-        <v>36.55633776984185</v>
+        <v>36.99407350470732</v>
       </c>
       <c r="I15" t="n">
-        <v>2.543584265913789</v>
+        <v>2.254442559190843</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727062461683597</v>
+        <v>4.725850112678973</v>
       </c>
       <c r="K15" t="n">
-        <v>16.86595432006217</v>
+        <v>18.86173941054846</v>
       </c>
       <c r="L15" t="n">
-        <v>43.78233209294969</v>
+        <v>43.93367598176011</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91530024077358</v>
+        <v>99.92492145043678</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.66201477812139</v>
+        <v>78.44749629912891</v>
       </c>
       <c r="C16" t="n">
-        <v>37.18830587317018</v>
+        <v>34.78624714466162</v>
       </c>
       <c r="D16" t="n">
-        <v>1.397606365677906</v>
+        <v>1.260082465968964</v>
       </c>
       <c r="E16" t="n">
-        <v>11.83688872868573</v>
+        <v>11.29891932672627</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569930746954816</v>
+        <v>0.7567401117766552</v>
       </c>
       <c r="G16" t="n">
-        <v>23.22942100264445</v>
+        <v>21.49829674054962</v>
       </c>
       <c r="H16" t="n">
-        <v>36.58838701665784</v>
+        <v>37.02362888625923</v>
       </c>
       <c r="I16" t="n">
-        <v>2.121511872913235</v>
+        <v>1.880203069244083</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731206716846763</v>
+        <v>4.729625698604098</v>
       </c>
       <c r="K16" t="n">
-        <v>19.33798522187859</v>
+        <v>21.55250370087108</v>
       </c>
       <c r="L16" t="n">
-        <v>43.4030537864536</v>
+        <v>43.59862575004533</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92934488150237</v>
+        <v>99.93737659557803</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.25587235848906</v>
+        <v>80.48292436191272</v>
       </c>
       <c r="C17" t="n">
-        <v>38.35065946692966</v>
+        <v>36.26253608592616</v>
       </c>
       <c r="D17" t="n">
-        <v>1.398812120241316</v>
+        <v>1.261040650605925</v>
       </c>
       <c r="E17" t="n">
-        <v>12.58987440119577</v>
+        <v>12.18531153745125</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576461540436437</v>
+        <v>0.7573155477253802</v>
       </c>
       <c r="G17" t="n">
-        <v>23.63741299068045</v>
+        <v>22.08644289856657</v>
       </c>
       <c r="H17" t="n">
-        <v>37.0079041627279</v>
+        <v>37.62358072775127</v>
       </c>
       <c r="I17" t="n">
-        <v>2.128934066827211</v>
+        <v>1.836010826528692</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735288462772775</v>
+        <v>4.733222173283629</v>
       </c>
       <c r="K17" t="n">
-        <v>17.74412764151094</v>
+        <v>19.51707563808729</v>
       </c>
       <c r="L17" t="n">
-        <v>43.8343095929474</v>
+        <v>44.15923441736651</v>
       </c>
       <c r="M17" t="n">
-        <v>99.929096701388</v>
+        <v>99.93884614137995</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.88515781975092</v>
+        <v>77.94023707782165</v>
       </c>
       <c r="C18" t="n">
-        <v>36.30871641448235</v>
+        <v>34.00242485394259</v>
       </c>
       <c r="D18" t="n">
-        <v>1.311647890281524</v>
+        <v>1.171568602147127</v>
       </c>
       <c r="E18" t="n">
-        <v>12.10126544272351</v>
+        <v>11.57592042374841</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582074367392069</v>
+        <v>0.7578114226663206</v>
       </c>
       <c r="G18" t="n">
-        <v>22.16449402482332</v>
+        <v>20.51938850713716</v>
       </c>
       <c r="H18" t="n">
-        <v>37.03532051810004</v>
+        <v>37.64821588931289</v>
       </c>
       <c r="I18" t="n">
-        <v>1.775426027463267</v>
+        <v>1.531010841145231</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738796479620045</v>
+        <v>4.736321391664506</v>
       </c>
       <c r="K18" t="n">
-        <v>20.1148421802491</v>
+        <v>22.05976292217836</v>
       </c>
       <c r="L18" t="n">
-        <v>43.51730434785668</v>
+        <v>43.88681192314215</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94086294258813</v>
+        <v>99.9489996992631</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.93561144020339</v>
+        <v>76.93776467953818</v>
       </c>
       <c r="C19" t="n">
-        <v>35.63265536327883</v>
+        <v>33.21083085861918</v>
       </c>
       <c r="D19" t="n">
-        <v>1.277438665298687</v>
+        <v>1.135920988501159</v>
       </c>
       <c r="E19" t="n">
-        <v>12.03239218784996</v>
+        <v>11.4403344721145</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586814457168699</v>
+        <v>0.7582381841508727</v>
       </c>
       <c r="G19" t="n">
-        <v>21.58641955198352</v>
+        <v>19.89503989245648</v>
       </c>
       <c r="H19" t="n">
-        <v>37.05847391064879</v>
+        <v>37.66941748119064</v>
       </c>
       <c r="I19" t="n">
-        <v>1.480446642975115</v>
+        <v>1.299825010181582</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741759035730438</v>
+        <v>4.738988650942957</v>
       </c>
       <c r="K19" t="n">
-        <v>21.0643885597966</v>
+        <v>23.06223532046183</v>
       </c>
       <c r="L19" t="n">
-        <v>43.2536386872728</v>
+        <v>43.68363070672734</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95068261034825</v>
+        <v>99.95669688580834</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.50166253183471</v>
+        <v>74.24467364715647</v>
       </c>
       <c r="C20" t="n">
-        <v>33.42660053178246</v>
+        <v>30.71697375625544</v>
       </c>
       <c r="D20" t="n">
-        <v>1.188978817958695</v>
+        <v>1.042217282700158</v>
       </c>
       <c r="E20" t="n">
-        <v>11.40490339489237</v>
+        <v>10.6772244228969</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590894947626347</v>
+        <v>0.7586071056731616</v>
       </c>
       <c r="G20" t="n">
-        <v>20.09160697893603</v>
+        <v>18.25387031829289</v>
       </c>
       <c r="H20" t="n">
-        <v>37.07840543131812</v>
+        <v>37.68774557272095</v>
       </c>
       <c r="I20" t="n">
-        <v>1.234369071700398</v>
+        <v>1.083714534415168</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744309342266468</v>
+        <v>4.741294410457263</v>
       </c>
       <c r="K20" t="n">
-        <v>23.4983374681653</v>
+        <v>25.7553263528435</v>
       </c>
       <c r="L20" t="n">
-        <v>43.03393848219183</v>
+        <v>43.49159364061824</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95887648213957</v>
+        <v>99.96389374971719</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.33368568152765</v>
+        <v>80.82109717611756</v>
       </c>
       <c r="C21" t="n">
-        <v>36.98243362221318</v>
+        <v>34.96236960187567</v>
       </c>
       <c r="D21" t="n">
-        <v>1.189871082983026</v>
+        <v>1.04281237554352</v>
       </c>
       <c r="E21" t="n">
-        <v>13.33818468947729</v>
+        <v>12.91512353778173</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759659150837481</v>
+        <v>0.7590402607042704</v>
       </c>
       <c r="G21" t="n">
-        <v>21.72247203777838</v>
+        <v>20.2653564972391</v>
       </c>
       <c r="H21" t="n">
-        <v>38.72201817405988</v>
+        <v>39.71032824783421</v>
       </c>
       <c r="I21" t="n">
-        <v>1.853610853657339</v>
+        <v>1.384434627613028</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747869692734257</v>
+        <v>4.744001629401693</v>
       </c>
       <c r="K21" t="n">
-        <v>17.66631431847233</v>
+        <v>19.17890282388244</v>
       </c>
       <c r="L21" t="n">
-        <v>45.28951136394964</v>
+        <v>45.81260608810479</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93825930463515</v>
+        <v>99.9538785138629</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_8_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.58336282495405</v>
+        <v>45.1579540302297</v>
       </c>
       <c r="M2" t="n">
-        <v>99.88509544642966</v>
+        <v>100.8476742474867</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99676142002549</v>
+        <v>88.1048125723549</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92663640213999</v>
+        <v>45.94478203132221</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228653782393305</v>
+        <v>2.228917072536643</v>
       </c>
       <c r="E3" t="n">
-        <v>5.703457350400984</v>
+        <v>5.719854966983703</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428845941311016</v>
+        <v>0.7429723575122146</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97274257733766</v>
+        <v>33.9778843794628</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17269133003067</v>
+        <v>34.17672844556186</v>
       </c>
       <c r="I3" t="n">
-        <v>6.533303072412396</v>
+        <v>6.614878115846337</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643028713319385</v>
+        <v>4.643577234451341</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00323857997449</v>
+        <v>11.89518742764509</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83560485601824</v>
+        <v>48.92261020099939</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7654798381327</v>
+        <v>106.7625796599667</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08402189117612</v>
+        <v>87.35436557044186</v>
       </c>
       <c r="C4" t="n">
-        <v>42.6424019799154</v>
+        <v>42.83791484622763</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184663724769492</v>
+        <v>2.193635821537929</v>
       </c>
       <c r="E4" t="n">
-        <v>6.500178389617345</v>
+        <v>6.549985760002065</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444359776731505</v>
+        <v>0.744538466103249</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30217502870246</v>
+        <v>33.44005267546277</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24405497296492</v>
+        <v>34.24876944074945</v>
       </c>
       <c r="I4" t="n">
-        <v>5.455788936991565</v>
+        <v>5.524017993441087</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652724860457191</v>
+        <v>4.653365413145305</v>
       </c>
       <c r="K4" t="n">
-        <v>12.91597810882386</v>
+        <v>12.64563442955815</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26013927036038</v>
+        <v>44.33270410988516</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81851935909965</v>
+        <v>99.81625338567093</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.82988322585027</v>
+        <v>86.29677862223051</v>
       </c>
       <c r="C5" t="n">
-        <v>42.23506291890764</v>
+        <v>42.63785049620593</v>
       </c>
       <c r="D5" t="n">
-        <v>2.123157379369241</v>
+        <v>2.142448679148357</v>
       </c>
       <c r="E5" t="n">
-        <v>7.07626316724916</v>
+        <v>7.165737231114595</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457527521597039</v>
+        <v>0.7458646936655512</v>
       </c>
       <c r="G5" t="n">
-        <v>32.36459591450213</v>
+        <v>32.65974961831554</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30462659934638</v>
+        <v>34.30977590861535</v>
       </c>
       <c r="I5" t="n">
-        <v>4.554532712225503</v>
+        <v>4.611548155961409</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66095470099815</v>
+        <v>4.661654335409694</v>
       </c>
       <c r="K5" t="n">
-        <v>14.17011677414972</v>
+        <v>13.7032213777695</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44327061424841</v>
+        <v>43.50548318176233</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84845030730578</v>
+        <v>99.84655505573775</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.33766347947692</v>
+        <v>85.10906450908998</v>
       </c>
       <c r="C6" t="n">
-        <v>41.45012345471599</v>
+        <v>42.16657890854262</v>
       </c>
       <c r="D6" t="n">
-        <v>2.050007587470439</v>
+        <v>2.084954369074717</v>
       </c>
       <c r="E6" t="n">
-        <v>7.465986840287051</v>
+        <v>7.61489725249832</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468731353862412</v>
+        <v>0.746988994761244</v>
       </c>
       <c r="G6" t="n">
-        <v>31.24952857232613</v>
+        <v>31.78329932582625</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35616422776709</v>
+        <v>34.36149375901722</v>
       </c>
       <c r="I6" t="n">
-        <v>3.801146020075959</v>
+        <v>3.848749590654456</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667957096164009</v>
+        <v>4.668681217257775</v>
       </c>
       <c r="K6" t="n">
-        <v>15.66233652052307</v>
+        <v>14.89093549091002</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76102522719911</v>
+        <v>42.81438704065955</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87348520243818</v>
+        <v>99.87190144011218</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.50025752565082</v>
+        <v>83.70813294425336</v>
       </c>
       <c r="C7" t="n">
-        <v>40.20292712887654</v>
+        <v>41.36375693158144</v>
       </c>
       <c r="D7" t="n">
-        <v>1.960117166540159</v>
+        <v>2.017119379356111</v>
       </c>
       <c r="E7" t="n">
-        <v>7.667225590464953</v>
+        <v>7.902375058492327</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478302407970989</v>
+        <v>0.7479442484567103</v>
       </c>
       <c r="G7" t="n">
-        <v>29.87927350868251</v>
+        <v>30.74921444849263</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40019107666654</v>
+        <v>34.40543542900867</v>
       </c>
       <c r="I7" t="n">
-        <v>3.171680937517698</v>
+        <v>3.211392827592466</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67393900498187</v>
+        <v>4.674651552854439</v>
       </c>
       <c r="K7" t="n">
-        <v>17.49974247434916</v>
+        <v>16.29186705574667</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19174300732773</v>
+        <v>42.23746630182038</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89441261055343</v>
+        <v>99.89309028914847</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.36462238972297</v>
+        <v>88.51646791844729</v>
       </c>
       <c r="C8" t="n">
-        <v>42.55308629697674</v>
+        <v>43.66378713560008</v>
       </c>
       <c r="D8" t="n">
-        <v>1.964278392752406</v>
+        <v>2.021371753036092</v>
       </c>
       <c r="E8" t="n">
-        <v>9.528300036599326</v>
+        <v>9.731290681024149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494178452798499</v>
+        <v>0.7495210209912371</v>
       </c>
       <c r="G8" t="n">
-        <v>30.40142799863235</v>
+        <v>31.25365313537214</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47322088287309</v>
+        <v>34.4779669655969</v>
       </c>
       <c r="I8" t="n">
-        <v>5.564115700586884</v>
+        <v>5.598157981231537</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683861532999064</v>
+        <v>4.684506381195231</v>
       </c>
       <c r="K8" t="n">
-        <v>12.63537761027703</v>
+        <v>11.48353208155272</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62645847948499</v>
+        <v>44.66646807958966</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81492238673877</v>
+        <v>99.81378729674246</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.06619463990621</v>
+        <v>86.64878412450777</v>
       </c>
       <c r="C9" t="n">
-        <v>41.11779037075092</v>
+        <v>42.66567473832181</v>
       </c>
       <c r="D9" t="n">
-        <v>1.859891614616718</v>
+        <v>1.937063715734942</v>
       </c>
       <c r="E9" t="n">
-        <v>9.796142311035021</v>
+        <v>10.10433464322803</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507819586759821</v>
+        <v>0.750868568549769</v>
       </c>
       <c r="G9" t="n">
-        <v>28.78581835225502</v>
+        <v>29.9501155004089</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53597009909517</v>
+        <v>34.53995415328937</v>
       </c>
       <c r="I9" t="n">
-        <v>4.645203062503418</v>
+        <v>4.673518989860696</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69238724172489</v>
+        <v>4.692928553436055</v>
       </c>
       <c r="K9" t="n">
-        <v>14.93380536009378</v>
+        <v>13.35121587549224</v>
       </c>
       <c r="L9" t="n">
-        <v>43.79384549969456</v>
+        <v>43.82760499781841</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84544123053925</v>
+        <v>99.84449561163247</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.56981517845034</v>
+        <v>84.57539724959541</v>
       </c>
       <c r="C10" t="n">
-        <v>39.34142186714126</v>
+        <v>41.31809541271218</v>
       </c>
       <c r="D10" t="n">
-        <v>1.747816269560844</v>
+        <v>1.844249468905316</v>
       </c>
       <c r="E10" t="n">
-        <v>9.852012738780223</v>
+        <v>10.27028402384271</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519570562494757</v>
+        <v>0.7520228946807834</v>
       </c>
       <c r="G10" t="n">
-        <v>27.05121161539443</v>
+        <v>28.51505820722323</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59002458747588</v>
+        <v>34.59305315531603</v>
       </c>
       <c r="I10" t="n">
-        <v>3.877061309430279</v>
+        <v>3.900586407872455</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699731601559225</v>
+        <v>4.700143091754895</v>
       </c>
       <c r="K10" t="n">
-        <v>17.43018482154963</v>
+        <v>15.42460275040458</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09935989290624</v>
+        <v>43.12748186494267</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87096658159714</v>
+        <v>99.87018002805942</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.83630572181285</v>
+        <v>82.29975527847805</v>
       </c>
       <c r="C11" t="n">
-        <v>37.20796896076833</v>
+        <v>39.64772073573917</v>
       </c>
       <c r="D11" t="n">
-        <v>1.626399776929112</v>
+        <v>1.743249059896164</v>
       </c>
       <c r="E11" t="n">
-        <v>9.706825780942523</v>
+        <v>10.25029371259494</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529727879731818</v>
+        <v>0.7530142561991223</v>
       </c>
       <c r="G11" t="n">
-        <v>25.17203055215532</v>
+        <v>26.95342970174842</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63674824676636</v>
+        <v>34.63865578515962</v>
       </c>
       <c r="I11" t="n">
-        <v>3.23524865221396</v>
+        <v>3.25477366163528</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706079924832388</v>
+        <v>4.706339101244513</v>
       </c>
       <c r="K11" t="n">
-        <v>20.16369427818715</v>
+        <v>17.70024472152195</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52064061356035</v>
+        <v>42.54368492029797</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89230385251582</v>
+        <v>99.8916503775591</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.11408679467996</v>
+        <v>79.89688362831504</v>
       </c>
       <c r="C12" t="n">
-        <v>34.98535006145252</v>
+        <v>37.74916697772497</v>
       </c>
       <c r="D12" t="n">
-        <v>1.506874263176921</v>
+        <v>1.63755063322854</v>
       </c>
       <c r="E12" t="n">
-        <v>9.443327191834486</v>
+        <v>10.08135162977233</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538513190797098</v>
+        <v>0.7538673236495781</v>
       </c>
       <c r="G12" t="n">
-        <v>23.32211644947812</v>
+        <v>25.3191622993952</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67716067766665</v>
+        <v>34.67789688788059</v>
       </c>
       <c r="I12" t="n">
-        <v>2.699186149195886</v>
+        <v>2.715384081578944</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711570744248188</v>
+        <v>4.711670772809861</v>
       </c>
       <c r="K12" t="n">
-        <v>22.88591320532004</v>
+        <v>20.10311637168496</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03886871511038</v>
+        <v>42.0573062711002</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91013198188296</v>
+        <v>99.90958962051013</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.51132304054471</v>
+        <v>77.53672268063514</v>
       </c>
       <c r="C13" t="n">
-        <v>32.79829243460011</v>
+        <v>35.80890761636283</v>
       </c>
       <c r="D13" t="n">
-        <v>1.393839340445018</v>
+        <v>1.534694628982911</v>
       </c>
       <c r="E13" t="n">
-        <v>9.110220947527038</v>
+        <v>9.825636925421787</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546106498360434</v>
+        <v>0.7546013961094442</v>
       </c>
       <c r="G13" t="n">
-        <v>21.57265818661464</v>
+        <v>23.72884331192795</v>
       </c>
       <c r="H13" t="n">
-        <v>34.712089892458</v>
+        <v>34.71166422103443</v>
       </c>
       <c r="I13" t="n">
-        <v>2.251587462188711</v>
+        <v>2.265023471474591</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716316561475273</v>
+        <v>4.716258725684024</v>
       </c>
       <c r="K13" t="n">
-        <v>25.48867695945527</v>
+        <v>22.46327731936486</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63805321291142</v>
+        <v>41.6523877286729</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92502260696681</v>
+        <v>99.92457266440059</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.07699792677528</v>
+        <v>84.17514985038341</v>
       </c>
       <c r="C14" t="n">
-        <v>37.67165429041095</v>
+        <v>39.86429327601153</v>
       </c>
       <c r="D14" t="n">
-        <v>1.395364494760864</v>
+        <v>1.536534553837597</v>
       </c>
       <c r="E14" t="n">
-        <v>11.76752408443074</v>
+        <v>12.10237648084732</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554363530975206</v>
+        <v>0.7555060776257942</v>
       </c>
       <c r="G14" t="n">
-        <v>23.79455009602101</v>
+        <v>25.51766893147875</v>
       </c>
       <c r="H14" t="n">
-        <v>36.94835911235665</v>
+        <v>36.51365699761023</v>
       </c>
       <c r="I14" t="n">
-        <v>2.694286579248989</v>
+        <v>3.027493823822492</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721477206859506</v>
+        <v>4.721912985161212</v>
       </c>
       <c r="K14" t="n">
-        <v>17.92300207322471</v>
+        <v>15.82485014961659</v>
       </c>
       <c r="L14" t="n">
-        <v>44.3156322469104</v>
+        <v>44.21006095609577</v>
       </c>
       <c r="M14" t="n">
-        <v>99.91028861054606</v>
+        <v>99.89920438172391</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.13826058945153</v>
+        <v>83.43512806587626</v>
       </c>
       <c r="C15" t="n">
-        <v>37.1295060581282</v>
+        <v>39.58199899726268</v>
       </c>
       <c r="D15" t="n">
-        <v>1.359556404257879</v>
+        <v>1.507773229080167</v>
       </c>
       <c r="E15" t="n">
-        <v>11.85277803730321</v>
+        <v>12.30731115057752</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561360180286354</v>
+        <v>0.7562683457358764</v>
       </c>
       <c r="G15" t="n">
-        <v>23.19542395328467</v>
+        <v>25.05058254301564</v>
       </c>
       <c r="H15" t="n">
-        <v>36.99407350470732</v>
+        <v>36.56105862434273</v>
       </c>
       <c r="I15" t="n">
-        <v>2.254442559190843</v>
+        <v>2.525457012275097</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725850112678973</v>
+        <v>4.726677160849225</v>
       </c>
       <c r="K15" t="n">
-        <v>18.86173941054846</v>
+        <v>16.56487193412375</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93367598176011</v>
+        <v>43.76903201795182</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92492145043678</v>
+        <v>99.91590294933825</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.44749629912891</v>
+        <v>81.03379281624264</v>
       </c>
       <c r="C16" t="n">
-        <v>34.78624714466162</v>
+        <v>37.57135793714715</v>
       </c>
       <c r="D16" t="n">
-        <v>1.260082465968964</v>
+        <v>1.415840387519518</v>
       </c>
       <c r="E16" t="n">
-        <v>11.29891932672627</v>
+        <v>11.90796432748061</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567401117766552</v>
+        <v>0.7569236203916162</v>
       </c>
       <c r="G16" t="n">
-        <v>21.49829674054962</v>
+        <v>23.52318360031524</v>
       </c>
       <c r="H16" t="n">
-        <v>37.02362888625923</v>
+        <v>36.59273724111762</v>
       </c>
       <c r="I16" t="n">
-        <v>1.880203069244083</v>
+        <v>2.106371011970434</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729625698604098</v>
+        <v>4.730772627447599</v>
       </c>
       <c r="K16" t="n">
-        <v>21.55250370087108</v>
+        <v>18.96620718375736</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59862575004533</v>
+        <v>43.3922832954212</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93737659557803</v>
+        <v>99.92984841632571</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.48292436191272</v>
+        <v>82.68538697909705</v>
       </c>
       <c r="C17" t="n">
-        <v>36.26253608592616</v>
+        <v>38.77384320720184</v>
       </c>
       <c r="D17" t="n">
-        <v>1.261040650605925</v>
+        <v>1.417044884551778</v>
       </c>
       <c r="E17" t="n">
-        <v>12.18531153745125</v>
+        <v>12.67941528845347</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573155477253802</v>
+        <v>0.757567557563098</v>
       </c>
       <c r="G17" t="n">
-        <v>22.08644289856657</v>
+        <v>23.95280152469658</v>
       </c>
       <c r="H17" t="n">
-        <v>37.62358072775127</v>
+        <v>37.0334738189235</v>
       </c>
       <c r="I17" t="n">
-        <v>1.836010826528692</v>
+        <v>2.110286670139261</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733222173283629</v>
+        <v>4.73479723476936</v>
       </c>
       <c r="K17" t="n">
-        <v>19.51707563808729</v>
+        <v>17.31461302090296</v>
       </c>
       <c r="L17" t="n">
-        <v>44.15923441736651</v>
+        <v>43.84126067478706</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93884614137995</v>
+        <v>99.92971690289184</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.94023707782165</v>
+        <v>80.30927282798554</v>
       </c>
       <c r="C18" t="n">
-        <v>34.00242485394259</v>
+        <v>36.72381047500608</v>
       </c>
       <c r="D18" t="n">
-        <v>1.171568602147127</v>
+        <v>1.32952319064137</v>
       </c>
       <c r="E18" t="n">
-        <v>11.57592042374841</v>
+        <v>12.18959930714544</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578114226663206</v>
+        <v>0.7581209226357641</v>
       </c>
       <c r="G18" t="n">
-        <v>20.51938850713716</v>
+        <v>22.47339195468543</v>
       </c>
       <c r="H18" t="n">
-        <v>37.64821588931289</v>
+        <v>37.06052491255377</v>
       </c>
       <c r="I18" t="n">
-        <v>1.531010841145231</v>
+        <v>1.759856773850252</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736321391664506</v>
+        <v>4.738255766473523</v>
       </c>
       <c r="K18" t="n">
-        <v>22.05976292217836</v>
+        <v>19.69072717201447</v>
       </c>
       <c r="L18" t="n">
-        <v>43.88681192314215</v>
+        <v>43.52684327880891</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9489996992631</v>
+        <v>99.94138092582946</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.93776467953818</v>
+        <v>79.37085946740417</v>
       </c>
       <c r="C19" t="n">
-        <v>33.21083085861918</v>
+        <v>36.05664656645029</v>
       </c>
       <c r="D19" t="n">
-        <v>1.135920988501159</v>
+        <v>1.295657253445181</v>
       </c>
       <c r="E19" t="n">
-        <v>11.4403344721145</v>
+        <v>12.12367806393806</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582381841508727</v>
+        <v>0.7585881408759908</v>
       </c>
       <c r="G19" t="n">
-        <v>19.89503989245648</v>
+        <v>21.90094426375379</v>
       </c>
       <c r="H19" t="n">
-        <v>37.66941748119064</v>
+        <v>37.08336474286912</v>
       </c>
       <c r="I19" t="n">
-        <v>1.299825010181582</v>
+        <v>1.4674511220471</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738988650942957</v>
+        <v>4.741175880474939</v>
       </c>
       <c r="K19" t="n">
-        <v>23.06223532046183</v>
+        <v>20.62914053259582</v>
       </c>
       <c r="L19" t="n">
-        <v>43.68363070672734</v>
+        <v>43.26532799056917</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95669688580834</v>
+        <v>99.95111508961529</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.24467364715647</v>
+        <v>76.84066983158819</v>
       </c>
       <c r="C20" t="n">
-        <v>30.71697375625544</v>
+        <v>33.75249074203689</v>
       </c>
       <c r="D20" t="n">
-        <v>1.042217282700158</v>
+        <v>1.203480484560421</v>
       </c>
       <c r="E20" t="n">
-        <v>10.6772244228969</v>
+        <v>11.46508570585627</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586071056731616</v>
+        <v>0.758990771215311</v>
       </c>
       <c r="G20" t="n">
-        <v>18.25387031829289</v>
+        <v>20.34284834572444</v>
       </c>
       <c r="H20" t="n">
-        <v>37.68774557272095</v>
+        <v>37.10304721208399</v>
       </c>
       <c r="I20" t="n">
-        <v>1.083714534415168</v>
+        <v>1.223524992052062</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741294410457263</v>
+        <v>4.743692320095691</v>
       </c>
       <c r="K20" t="n">
-        <v>25.7553263528435</v>
+        <v>23.15933016841183</v>
       </c>
       <c r="L20" t="n">
-        <v>43.49159364061824</v>
+        <v>43.0474165583833</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96389374971719</v>
+        <v>99.95923746883201</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.82109717611756</v>
+        <v>82.6663018037265</v>
       </c>
       <c r="C21" t="n">
-        <v>34.96236960187567</v>
+        <v>37.27348241844192</v>
       </c>
       <c r="D21" t="n">
-        <v>1.04281237554352</v>
+        <v>1.20439786624512</v>
       </c>
       <c r="E21" t="n">
-        <v>12.91512353778173</v>
+        <v>13.38423484558401</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590402607042704</v>
+        <v>0.7595693300214582</v>
       </c>
       <c r="G21" t="n">
-        <v>20.2653564972391</v>
+        <v>21.95369297699019</v>
       </c>
       <c r="H21" t="n">
-        <v>39.71032824783421</v>
+        <v>38.72666770442033</v>
       </c>
       <c r="I21" t="n">
-        <v>1.384434627613028</v>
+        <v>1.890430767831289</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744001629401693</v>
+        <v>4.747308312634111</v>
       </c>
       <c r="K21" t="n">
-        <v>19.17890282388244</v>
+        <v>17.33369819627351</v>
       </c>
       <c r="L21" t="n">
-        <v>45.81260608810479</v>
+        <v>45.32985302396663</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9538785138629</v>
+        <v>99.93703363868205</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_8_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.1579540302297</v>
+        <v>43.78746394363518</v>
       </c>
       <c r="M2" t="n">
-        <v>100.8476742474867</v>
+        <v>95.91290670233226</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.1048125723549</v>
+        <v>81.51955726652946</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94478203132221</v>
+        <v>43.27511282208501</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228917072536643</v>
+        <v>2.182765363072852</v>
       </c>
       <c r="E3" t="n">
-        <v>5.719854966983703</v>
+        <v>4.150208292686522</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429723575122146</v>
+        <v>0.7376630700937464</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9778843794628</v>
+        <v>32.83242900288749</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17672844556186</v>
+        <v>33.93250122431233</v>
       </c>
       <c r="I3" t="n">
-        <v>6.614878115846337</v>
+        <v>3.07359612539061</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643577234451341</v>
+        <v>4.610394188085915</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89518742764509</v>
+        <v>18.48044273347054</v>
       </c>
       <c r="L3" t="n">
-        <v>48.92261020099939</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7625796599667</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.35436557044186</v>
+        <v>88.51501183227246</v>
       </c>
       <c r="C4" t="n">
-        <v>42.83791484622763</v>
+        <v>42.7722244543947</v>
       </c>
       <c r="D4" t="n">
-        <v>2.193635821537929</v>
+        <v>2.188507789650731</v>
       </c>
       <c r="E4" t="n">
-        <v>6.549985760002065</v>
+        <v>6.46704061312806</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744538466103249</v>
+        <v>0.7396037166198867</v>
       </c>
       <c r="G4" t="n">
-        <v>33.44005267546277</v>
+        <v>33.48959764928642</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24876944074945</v>
+        <v>34.02177096451479</v>
       </c>
       <c r="I4" t="n">
-        <v>5.524017993441087</v>
+        <v>6.985967870198288</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653365413145305</v>
+        <v>4.622523228874292</v>
       </c>
       <c r="K4" t="n">
-        <v>12.64563442955815</v>
+        <v>11.48498816772756</v>
       </c>
       <c r="L4" t="n">
-        <v>44.33270410988516</v>
+        <v>45.51053279834615</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81625338567093</v>
+        <v>99.7677454204684</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.29677862223051</v>
+        <v>87.33698741711828</v>
       </c>
       <c r="C5" t="n">
-        <v>42.63785049620593</v>
+        <v>42.67699866883624</v>
       </c>
       <c r="D5" t="n">
-        <v>2.142448679148357</v>
+        <v>2.132072754851502</v>
       </c>
       <c r="E5" t="n">
-        <v>7.165737231114595</v>
+        <v>7.27270905600422</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458646936655512</v>
+        <v>0.7412507067485348</v>
       </c>
       <c r="G5" t="n">
-        <v>32.65974961831554</v>
+        <v>32.62600163300205</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30977590861535</v>
+        <v>34.0975325104326</v>
       </c>
       <c r="I5" t="n">
-        <v>4.611548155961409</v>
+        <v>5.834603838901036</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661654335409694</v>
+        <v>4.632816917178343</v>
       </c>
       <c r="K5" t="n">
-        <v>13.7032213777695</v>
+        <v>12.66301258288173</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50548318176233</v>
+        <v>44.46593408522099</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84655505573775</v>
+        <v>99.80594533693895</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.10906450908998</v>
+        <v>85.94477530966424</v>
       </c>
       <c r="C6" t="n">
-        <v>42.16657890854262</v>
+        <v>42.19018368744408</v>
       </c>
       <c r="D6" t="n">
-        <v>2.084954369074717</v>
+        <v>2.06534553905602</v>
       </c>
       <c r="E6" t="n">
-        <v>7.61489725249832</v>
+        <v>7.856988674876225</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746988994761244</v>
+        <v>0.7426511782204761</v>
       </c>
       <c r="G6" t="n">
-        <v>31.78329932582625</v>
+        <v>31.60490971831234</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36149375901722</v>
+        <v>34.16195419814191</v>
       </c>
       <c r="I6" t="n">
-        <v>3.848749590654456</v>
+        <v>4.871356137179307</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668681217257775</v>
+        <v>4.641569863877977</v>
       </c>
       <c r="K6" t="n">
-        <v>14.89093549091002</v>
+        <v>14.05522469033576</v>
       </c>
       <c r="L6" t="n">
-        <v>42.81438704065955</v>
+        <v>43.59251929336181</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87190144011218</v>
+        <v>99.83792767114164</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.70813294425336</v>
+        <v>84.25531745845257</v>
       </c>
       <c r="C7" t="n">
-        <v>41.36375693158144</v>
+        <v>41.25701450052829</v>
       </c>
       <c r="D7" t="n">
-        <v>2.017119379356111</v>
+        <v>1.984507991505109</v>
       </c>
       <c r="E7" t="n">
-        <v>7.902375058492327</v>
+        <v>8.227132014015741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479442484567103</v>
+        <v>0.7438458070207205</v>
       </c>
       <c r="G7" t="n">
-        <v>30.74921444849263</v>
+        <v>30.36789472789866</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40543542900867</v>
+        <v>34.21690712295315</v>
       </c>
       <c r="I7" t="n">
-        <v>3.211392827592466</v>
+        <v>4.065993501179697</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674651552854439</v>
+        <v>4.649036293879504</v>
       </c>
       <c r="K7" t="n">
-        <v>16.29186705574667</v>
+        <v>15.74468254154744</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23746630182038</v>
+        <v>42.8629875096693</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89309028914847</v>
+        <v>99.86468455174503</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.51646791844729</v>
+        <v>82.51108411323855</v>
       </c>
       <c r="C8" t="n">
-        <v>43.66378713560008</v>
+        <v>40.1438685148345</v>
       </c>
       <c r="D8" t="n">
-        <v>2.021371753036092</v>
+        <v>1.90181099799045</v>
       </c>
       <c r="E8" t="n">
-        <v>9.731290681024149</v>
+        <v>8.44979226102188</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495210209912371</v>
+        <v>0.7448654067022036</v>
       </c>
       <c r="G8" t="n">
-        <v>31.25365313537214</v>
+        <v>29.10242560199093</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4779669655969</v>
+        <v>34.26380870830137</v>
       </c>
       <c r="I8" t="n">
-        <v>5.598157981231537</v>
+        <v>3.392972345342945</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684506381195231</v>
+        <v>4.655408791888773</v>
       </c>
       <c r="K8" t="n">
-        <v>11.48353208155272</v>
+        <v>17.48891588676145</v>
       </c>
       <c r="L8" t="n">
-        <v>44.66646807958966</v>
+        <v>42.2542713344824</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81378729674246</v>
+        <v>99.88705573607834</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.64878412450777</v>
+        <v>80.65538129436661</v>
       </c>
       <c r="C9" t="n">
-        <v>42.66567473832181</v>
+        <v>38.81443760790894</v>
       </c>
       <c r="D9" t="n">
-        <v>1.937063715734942</v>
+        <v>1.814480455137716</v>
       </c>
       <c r="E9" t="n">
-        <v>10.10433464322803</v>
+        <v>8.533578021384722</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750868568549769</v>
+        <v>0.7457368318000137</v>
       </c>
       <c r="G9" t="n">
-        <v>29.9501155004089</v>
+        <v>27.76605167795817</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53995415328937</v>
+        <v>34.30389426280063</v>
       </c>
       <c r="I9" t="n">
-        <v>4.673518989860696</v>
+        <v>2.830784846535264</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692928553436055</v>
+        <v>4.660855198750085</v>
       </c>
       <c r="K9" t="n">
-        <v>13.35121587549224</v>
+        <v>19.34461870563339</v>
       </c>
       <c r="L9" t="n">
-        <v>43.82760499781841</v>
+        <v>41.74669445464259</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84449561163247</v>
+        <v>99.90575076818493</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.57539724959541</v>
+        <v>85.52147938207933</v>
       </c>
       <c r="C10" t="n">
-        <v>41.31809541271218</v>
+        <v>42.13787803690156</v>
       </c>
       <c r="D10" t="n">
-        <v>1.844249468905316</v>
+        <v>1.816552251472848</v>
       </c>
       <c r="E10" t="n">
-        <v>10.27028402384271</v>
+        <v>10.42833246061511</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520228946807834</v>
+        <v>0.7465883233830293</v>
       </c>
       <c r="G10" t="n">
-        <v>28.51505820722323</v>
+        <v>29.19451855428802</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59305315531603</v>
+        <v>35.7398261290501</v>
       </c>
       <c r="I10" t="n">
-        <v>3.900586407872455</v>
+        <v>2.929484642126281</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700143091754895</v>
+        <v>4.666177021143932</v>
       </c>
       <c r="K10" t="n">
-        <v>15.42460275040458</v>
+        <v>14.47852061792068</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12748186494267</v>
+        <v>43.28606322734208</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87018002805942</v>
+        <v>99.90246188216432</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.29975527847805</v>
+        <v>85.28631153700402</v>
       </c>
       <c r="C11" t="n">
-        <v>39.64772073573917</v>
+        <v>42.29101194425014</v>
       </c>
       <c r="D11" t="n">
-        <v>1.743249059896164</v>
+        <v>1.80379885088229</v>
       </c>
       <c r="E11" t="n">
-        <v>10.25029371259494</v>
+        <v>10.78158655394451</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530142561991223</v>
+        <v>0.7473173745761035</v>
       </c>
       <c r="G11" t="n">
-        <v>26.95342970174842</v>
+        <v>28.99960677391586</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63865578515962</v>
+        <v>35.78477952402523</v>
       </c>
       <c r="I11" t="n">
-        <v>3.25477366163528</v>
+        <v>2.498488868559385</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706339101244513</v>
+        <v>4.670733591100646</v>
       </c>
       <c r="K11" t="n">
-        <v>17.70024472152195</v>
+        <v>14.71368846299597</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54368492029797</v>
+        <v>42.91209787780083</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8916503775591</v>
+        <v>99.91679828504694</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.89688362831504</v>
+        <v>83.5190576771123</v>
       </c>
       <c r="C12" t="n">
-        <v>37.74916697772497</v>
+        <v>40.91206803628251</v>
       </c>
       <c r="D12" t="n">
-        <v>1.63755063322854</v>
+        <v>1.728578507767115</v>
       </c>
       <c r="E12" t="n">
-        <v>10.08135162977233</v>
+        <v>10.679283794727</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538673236495781</v>
+        <v>0.7479388950661767</v>
       </c>
       <c r="G12" t="n">
-        <v>25.3191622993952</v>
+        <v>27.79029212629196</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67789688788059</v>
+        <v>35.81454060608164</v>
       </c>
       <c r="I12" t="n">
-        <v>2.715384081578944</v>
+        <v>2.083805653014814</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711670772809861</v>
+        <v>4.674618094163604</v>
       </c>
       <c r="K12" t="n">
-        <v>20.10311637168496</v>
+        <v>16.48094232288769</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0573062711002</v>
+        <v>42.5375871722587</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90958962051013</v>
+        <v>99.9305975314289</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.53672268063514</v>
+        <v>84.75664883308585</v>
       </c>
       <c r="C13" t="n">
-        <v>35.80890761636283</v>
+        <v>41.93754846878201</v>
       </c>
       <c r="D13" t="n">
-        <v>1.534694628982911</v>
+        <v>1.729892069222895</v>
       </c>
       <c r="E13" t="n">
-        <v>9.825636925421787</v>
+        <v>11.34452159218533</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546013961094442</v>
+        <v>0.7485072601704652</v>
       </c>
       <c r="G13" t="n">
-        <v>23.72884331192795</v>
+        <v>28.14649624565757</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71166422103443</v>
+        <v>36.17684241986338</v>
       </c>
       <c r="I13" t="n">
-        <v>2.265023471474591</v>
+        <v>1.9322188699208</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716258725684024</v>
+        <v>4.678170376065407</v>
       </c>
       <c r="K13" t="n">
-        <v>22.46327731936486</v>
+        <v>15.24335116691416</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6523877286729</v>
+        <v>42.75474197512509</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92457266440059</v>
+        <v>99.93564161082126</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.17514985038341</v>
+        <v>82.95915714390331</v>
       </c>
       <c r="C14" t="n">
-        <v>39.86429327601153</v>
+        <v>40.44028920998718</v>
       </c>
       <c r="D14" t="n">
-        <v>1.536534553837597</v>
+        <v>1.655528953772515</v>
       </c>
       <c r="E14" t="n">
-        <v>12.10237648084732</v>
+        <v>11.12539050510235</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555060776257942</v>
+        <v>0.7489918413852746</v>
       </c>
       <c r="G14" t="n">
-        <v>25.51766893147875</v>
+        <v>26.93655882408204</v>
       </c>
       <c r="H14" t="n">
-        <v>36.51365699761023</v>
+        <v>36.20026319235367</v>
       </c>
       <c r="I14" t="n">
-        <v>3.027493823822492</v>
+        <v>1.611224818549484</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721912985161212</v>
+        <v>4.681199008657966</v>
       </c>
       <c r="K14" t="n">
-        <v>15.82485014961659</v>
+        <v>17.04084285609669</v>
       </c>
       <c r="L14" t="n">
-        <v>44.21006095609577</v>
+        <v>42.46519518752945</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89920438172391</v>
+        <v>99.94632725361332</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.43512806587626</v>
+        <v>82.20892518327199</v>
       </c>
       <c r="C15" t="n">
-        <v>39.58199899726268</v>
+        <v>39.92224920964713</v>
       </c>
       <c r="D15" t="n">
-        <v>1.507773229080167</v>
+        <v>1.624292760374881</v>
       </c>
       <c r="E15" t="n">
-        <v>12.30731115057752</v>
+        <v>11.1422512574273</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562683457358764</v>
+        <v>0.7494050585504636</v>
       </c>
       <c r="G15" t="n">
-        <v>25.05058254301564</v>
+        <v>26.42832515110492</v>
       </c>
       <c r="H15" t="n">
-        <v>36.56105862434273</v>
+        <v>36.22023479859677</v>
       </c>
       <c r="I15" t="n">
-        <v>2.525457012275097</v>
+        <v>1.360634541277255</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726677160849225</v>
+        <v>4.683781615940397</v>
       </c>
       <c r="K15" t="n">
-        <v>16.56487193412375</v>
+        <v>17.79107481672802</v>
       </c>
       <c r="L15" t="n">
-        <v>43.76903201795182</v>
+        <v>42.24134649708893</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91590294933825</v>
+        <v>99.95467052346407</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.03379281624264</v>
+        <v>80.07857193496457</v>
       </c>
       <c r="C16" t="n">
-        <v>37.57135793714715</v>
+        <v>38.00289799877199</v>
       </c>
       <c r="D16" t="n">
-        <v>1.415840387519518</v>
+        <v>1.536733108636967</v>
       </c>
       <c r="E16" t="n">
-        <v>11.90796432748061</v>
+        <v>10.73067970648351</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569236203916162</v>
+        <v>0.749758929016474</v>
       </c>
       <c r="G16" t="n">
-        <v>23.52318360031524</v>
+        <v>25.00367129393139</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59273724111762</v>
+        <v>36.23733806100599</v>
       </c>
       <c r="I16" t="n">
-        <v>2.106371011970434</v>
+        <v>1.134397529537272</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730772627447599</v>
+        <v>4.685993306352962</v>
       </c>
       <c r="K16" t="n">
-        <v>18.96620718375736</v>
+        <v>19.92142806503543</v>
       </c>
       <c r="L16" t="n">
-        <v>43.3922832954212</v>
+        <v>42.03787853226822</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92984841632571</v>
+        <v>99.96220459607564</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.68538697909705</v>
+        <v>84.56373540920134</v>
       </c>
       <c r="C17" t="n">
-        <v>38.77384320720184</v>
+        <v>40.94550815104745</v>
       </c>
       <c r="D17" t="n">
-        <v>1.417044884551778</v>
+        <v>1.537519431383255</v>
       </c>
       <c r="E17" t="n">
-        <v>12.67941528845347</v>
+        <v>12.3074261540764</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757567557563098</v>
+        <v>0.7501425691533362</v>
       </c>
       <c r="G17" t="n">
-        <v>23.95280152469658</v>
+        <v>26.37137118453377</v>
       </c>
       <c r="H17" t="n">
-        <v>37.0334738189235</v>
+        <v>37.61078604648153</v>
       </c>
       <c r="I17" t="n">
-        <v>2.110286670139261</v>
+        <v>1.298098966364707</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73479723476936</v>
+        <v>4.688391057208351</v>
       </c>
       <c r="K17" t="n">
-        <v>17.31461302090296</v>
+        <v>15.43626459079866</v>
       </c>
       <c r="L17" t="n">
-        <v>43.84126067478706</v>
+        <v>43.57497942186248</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92971690289184</v>
+        <v>99.95675216370859</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.30927282798554</v>
+        <v>86.24193493484083</v>
       </c>
       <c r="C18" t="n">
-        <v>36.72381047500608</v>
+        <v>41.69274821172366</v>
       </c>
       <c r="D18" t="n">
-        <v>1.32952319064137</v>
+        <v>1.53881449307541</v>
       </c>
       <c r="E18" t="n">
-        <v>12.18959930714544</v>
+        <v>12.92346334314478</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581209226357641</v>
+        <v>0.7507744186669979</v>
       </c>
       <c r="G18" t="n">
-        <v>22.47339195468543</v>
+        <v>26.51481400474373</v>
       </c>
       <c r="H18" t="n">
-        <v>37.06052491255377</v>
+        <v>37.64246583356351</v>
       </c>
       <c r="I18" t="n">
-        <v>1.759856773850252</v>
+        <v>2.179262724977683</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738255766473523</v>
+        <v>4.692340116668737</v>
       </c>
       <c r="K18" t="n">
-        <v>19.69072717201447</v>
+        <v>13.75806506515916</v>
       </c>
       <c r="L18" t="n">
-        <v>43.52684327880891</v>
+        <v>44.47660576765178</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94138092582946</v>
+        <v>99.9274190445346</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.37085946740417</v>
+        <v>83.82834747385822</v>
       </c>
       <c r="C19" t="n">
-        <v>36.05664656645029</v>
+        <v>39.61695417711743</v>
       </c>
       <c r="D19" t="n">
-        <v>1.295657253445181</v>
+        <v>1.449223468965637</v>
       </c>
       <c r="E19" t="n">
-        <v>12.12367806393806</v>
+        <v>12.47394296487204</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585881408759908</v>
+        <v>0.7513169681852659</v>
       </c>
       <c r="G19" t="n">
-        <v>21.90094426375379</v>
+        <v>24.97110009286241</v>
       </c>
       <c r="H19" t="n">
-        <v>37.08336474286912</v>
+        <v>37.66966828105856</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4674511220471</v>
+        <v>1.817364646756406</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741175880474939</v>
+        <v>4.695731051157912</v>
       </c>
       <c r="K19" t="n">
-        <v>20.62914053259582</v>
+        <v>16.17165252614178</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26532799056917</v>
+        <v>44.15085822104698</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95111508961529</v>
+        <v>99.93946492430618</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.84066983158819</v>
+        <v>81.40434366973355</v>
       </c>
       <c r="C20" t="n">
-        <v>33.75249074203689</v>
+        <v>37.47399144725462</v>
       </c>
       <c r="D20" t="n">
-        <v>1.203480484560421</v>
+        <v>1.359746885481636</v>
       </c>
       <c r="E20" t="n">
-        <v>11.46508570585627</v>
+        <v>11.9563569721107</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758990771215311</v>
+        <v>0.7517831814234577</v>
       </c>
       <c r="G20" t="n">
-        <v>20.34284834572444</v>
+        <v>23.42935807032873</v>
       </c>
       <c r="H20" t="n">
-        <v>37.10304721208399</v>
+        <v>37.69304336610868</v>
       </c>
       <c r="I20" t="n">
-        <v>1.223524992052062</v>
+        <v>1.515410310383744</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743692320095691</v>
+        <v>4.698644883896611</v>
       </c>
       <c r="K20" t="n">
-        <v>23.15933016841183</v>
+        <v>18.59565633026645</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0474165583833</v>
+        <v>43.87986987118015</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95923746883201</v>
+        <v>99.94951764870122</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.6663018037265</v>
+        <v>78.90503981669316</v>
       </c>
       <c r="C21" t="n">
-        <v>37.27348241844192</v>
+        <v>35.20841491052409</v>
       </c>
       <c r="D21" t="n">
-        <v>1.20439786624512</v>
+        <v>1.267937861216355</v>
       </c>
       <c r="E21" t="n">
-        <v>13.38423484558401</v>
+        <v>11.35965929262461</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595693300214582</v>
+        <v>0.7521844612721954</v>
       </c>
       <c r="G21" t="n">
-        <v>21.95369297699019</v>
+        <v>21.84742651632715</v>
       </c>
       <c r="H21" t="n">
-        <v>38.72666770442033</v>
+        <v>37.71316280894029</v>
       </c>
       <c r="I21" t="n">
-        <v>1.890430767831289</v>
+        <v>1.263515993361336</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747308312634111</v>
+        <v>4.701152882951222</v>
       </c>
       <c r="K21" t="n">
-        <v>17.33369819627351</v>
+        <v>21.09496018330685</v>
       </c>
       <c r="L21" t="n">
-        <v>45.32985302396663</v>
+        <v>43.65453017532507</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93703363868205</v>
+        <v>99.95790526915602</v>
       </c>
     </row>
   </sheetData>
